--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -1,103 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TracePatch" sheetId="1" r:id="rId1"/>
+    <sheet name="TracePatch" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>TracePatch</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>02541cd646efb3ad</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>trace_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>patch</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;TraceNode.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>union&lt;BuildPatch&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -410,106 +407,946 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TracePatch</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>02541cd646efb3ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>trace_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>trace_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;TraceNode.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>union&lt;BuildPatch&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>22009</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24701}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>22010</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24702}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>22011</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24703}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>22012</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24704}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>22013</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24705}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>22014</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24706}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>22015</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24707}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>22016</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24708}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>22017</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24709}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>22018</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24710}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>22029</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24711}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>22030</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24712}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>22031</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24713}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>22032</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24714}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>22033</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24715}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>22034</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24716}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>22035</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24717}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>22036</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24718}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>22037</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24719}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>22038</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24720}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>22047</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24721}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>22048</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24722}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>22049</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24723}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>22050</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24724}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>22051</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24725}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>22052</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24726}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>22053</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24727}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>22054</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24728}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>22055</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24729}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>22056</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24730}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>22068</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24731}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>22069</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24732}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>22070</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24733}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>22071</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24734}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>22072</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24735}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>22073</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24736}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>22074</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24737}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>22075</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24738}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>22076</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24739}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>22077</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24740}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>22088</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24741}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>22089</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24742}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>22090</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24743}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>22091</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24744}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>22092</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24745}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>22093</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24746}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>22094</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24747}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>22095</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24748}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>22096</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24749}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>22097</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24750}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>22106</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24751}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>22107</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24752}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>22108</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24753}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>22109</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24754}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>22110</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24755}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>22111</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24756}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>22112</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24757}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>22113</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24758}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>22114</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24759}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>22115</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":24760}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,6 +1349,1098 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>32009</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>32010</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>32011</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>32012</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>32013</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>32014</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>32015</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>32016</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>32017</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>32018</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>32027</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>32028</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>32029</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>32030</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>32031</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>32032</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>32033</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>32034</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>32035</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>32036</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>32037</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":30019,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>32038</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":30016,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>32039</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":30021,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>32040</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":30020,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>32045</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>32046</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>32047</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>32048</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>32049</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>32050</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>32051</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>32052</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>32053</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>32054</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>32063</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>32064</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>32065</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>32066</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>32067</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>32068</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>32069</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>32070</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>32071</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>32072</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>32081</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>32082</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>32083</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>32084</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>32085</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>32086</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>32087</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>32088</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>32089</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>32090</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>32099</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>32100</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>32101</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>32102</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>32103</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>32104</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>32105</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>32106</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>32107</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>32108</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>32117</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>32118</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>32119</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>32120</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>32121</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>32122</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>32123</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>32124</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>32125</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>32126</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>32135</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>32136</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>32137</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>32138</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>32139</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>32140</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>32141</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>32142</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>32143</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>32144</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":34081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2441,6 +2441,1046 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>42012</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>42013</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>42014</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>42015</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>42016</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>42017</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>42018</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>42019</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>42020</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>42021</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>42030</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>42031</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>42032</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>42033</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>42034</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>42035</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>42036</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>42037</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>42038</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>42039</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>42048</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>42049</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>42050</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>42051</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>42052</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>42053</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>42054</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>42055</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>42056</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>42057</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>42066</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>42067</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>42068</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>42069</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>42070</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>42071</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>42072</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>42073</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>42074</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>42075</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>42084</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>42085</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>42086</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>42087</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>42088</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>42089</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>42090</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>42091</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>42092</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>42093</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>42104</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>42105</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>42106</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>42107</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>42108</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>42109</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>42110</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>42111</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>42112</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>42113</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>42122</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>42123</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>42124</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>42125</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>42126</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>42127</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>42128</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>42129</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>42130</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>42131</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>42140</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>42141</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>42142</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>42143</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>42144</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>42145</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>42146</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>42147</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>42148</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>42149</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":44081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J231"/>
+  <dimension ref="A1:J311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3481,6 +3481,1046 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>52009</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>52010</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>52011</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>52012</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>52013</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>52014</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>52015</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>52016</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>52017</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>52018</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>52027</v>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>52028</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>52029</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>52030</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>52031</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>52032</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>52033</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>52034</v>
+      </c>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>52035</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>52036</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>52045</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>52046</v>
+      </c>
+      <c r="C253" t="n">
+        <v>1</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>52047</v>
+      </c>
+      <c r="C254" t="n">
+        <v>1</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>52048</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>52049</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>52050</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>52051</v>
+      </c>
+      <c r="C258" t="n">
+        <v>1</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>52052</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>52053</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>52054</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>52063</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>52064</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>52065</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>52066</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>52067</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>52068</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>52069</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>52070</v>
+      </c>
+      <c r="C269" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>52071</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>52072</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>52081</v>
+      </c>
+      <c r="C272" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>52082</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>52083</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>52084</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>52085</v>
+      </c>
+      <c r="C276" t="n">
+        <v>1</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>52086</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>52087</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>52088</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>52089</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>52090</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>52100</v>
+      </c>
+      <c r="C282" t="n">
+        <v>1</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>52101</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>52102</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>52103</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>52104</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>52105</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>52106</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>52107</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>52108</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>52109</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>52120</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>52121</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>52122</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>52123</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>52124</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>52125</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>52126</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>52127</v>
+      </c>
+      <c r="C299" t="n">
+        <v>1</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>52128</v>
+      </c>
+      <c r="C300" t="n">
+        <v>1</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>52129</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>52138</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>52139</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>52140</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>52141</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>52142</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>52143</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>52144</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>52145</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>52146</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>52147</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":54081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J311"/>
+  <dimension ref="A1:J391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4521,6 +4521,1046 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>62009</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>62010</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>62011</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>62012</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>62013</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>62014</v>
+      </c>
+      <c r="C317" t="n">
+        <v>1</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>62015</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>62016</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>62017</v>
+      </c>
+      <c r="C320" t="n">
+        <v>1</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>62018</v>
+      </c>
+      <c r="C321" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>62027</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>62028</v>
+      </c>
+      <c r="C323" t="n">
+        <v>1</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>62029</v>
+      </c>
+      <c r="C324" t="n">
+        <v>1</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>62030</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>62031</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>62032</v>
+      </c>
+      <c r="C327" t="n">
+        <v>1</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>62033</v>
+      </c>
+      <c r="C328" t="n">
+        <v>1</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>62034</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>62035</v>
+      </c>
+      <c r="C330" t="n">
+        <v>1</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>62036</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>62045</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>62046</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>62047</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>62048</v>
+      </c>
+      <c r="C335" t="n">
+        <v>1</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>62049</v>
+      </c>
+      <c r="C336" t="n">
+        <v>1</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>62050</v>
+      </c>
+      <c r="C337" t="n">
+        <v>1</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>62051</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>62052</v>
+      </c>
+      <c r="C339" t="n">
+        <v>1</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>62053</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>62054</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>62063</v>
+      </c>
+      <c r="C342" t="n">
+        <v>1</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>62064</v>
+      </c>
+      <c r="C343" t="n">
+        <v>1</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>62065</v>
+      </c>
+      <c r="C344" t="n">
+        <v>1</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>62066</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>62067</v>
+      </c>
+      <c r="C346" t="n">
+        <v>1</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>62068</v>
+      </c>
+      <c r="C347" t="n">
+        <v>1</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>62069</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>62070</v>
+      </c>
+      <c r="C349" t="n">
+        <v>1</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>62071</v>
+      </c>
+      <c r="C350" t="n">
+        <v>1</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>62072</v>
+      </c>
+      <c r="C351" t="n">
+        <v>1</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>62081</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>62082</v>
+      </c>
+      <c r="C353" t="n">
+        <v>1</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>62083</v>
+      </c>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>62084</v>
+      </c>
+      <c r="C355" t="n">
+        <v>1</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>62085</v>
+      </c>
+      <c r="C356" t="n">
+        <v>1</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>62086</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>62087</v>
+      </c>
+      <c r="C358" t="n">
+        <v>1</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>62088</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>62089</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>62090</v>
+      </c>
+      <c r="C361" t="n">
+        <v>1</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="n">
+        <v>62099</v>
+      </c>
+      <c r="C362" t="n">
+        <v>1</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="n">
+        <v>62100</v>
+      </c>
+      <c r="C363" t="n">
+        <v>1</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="n">
+        <v>62101</v>
+      </c>
+      <c r="C364" t="n">
+        <v>1</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="n">
+        <v>62102</v>
+      </c>
+      <c r="C365" t="n">
+        <v>1</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>62103</v>
+      </c>
+      <c r="C366" t="n">
+        <v>1</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>62104</v>
+      </c>
+      <c r="C367" t="n">
+        <v>1</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>62105</v>
+      </c>
+      <c r="C368" t="n">
+        <v>1</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>62106</v>
+      </c>
+      <c r="C369" t="n">
+        <v>1</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>62107</v>
+      </c>
+      <c r="C370" t="n">
+        <v>1</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>62108</v>
+      </c>
+      <c r="C371" t="n">
+        <v>1</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>62117</v>
+      </c>
+      <c r="C372" t="n">
+        <v>1</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>62118</v>
+      </c>
+      <c r="C373" t="n">
+        <v>1</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>62119</v>
+      </c>
+      <c r="C374" t="n">
+        <v>1</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>62120</v>
+      </c>
+      <c r="C375" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>62121</v>
+      </c>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>62122</v>
+      </c>
+      <c r="C377" t="n">
+        <v>1</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>62123</v>
+      </c>
+      <c r="C378" t="n">
+        <v>1</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>62124</v>
+      </c>
+      <c r="C379" t="n">
+        <v>1</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>62125</v>
+      </c>
+      <c r="C380" t="n">
+        <v>1</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>62126</v>
+      </c>
+      <c r="C381" t="n">
+        <v>1</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>62135</v>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>62136</v>
+      </c>
+      <c r="C383" t="n">
+        <v>1</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>62137</v>
+      </c>
+      <c r="C384" t="n">
+        <v>1</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>62138</v>
+      </c>
+      <c r="C385" t="n">
+        <v>1</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>62139</v>
+      </c>
+      <c r="C386" t="n">
+        <v>1</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>62140</v>
+      </c>
+      <c r="C387" t="n">
+        <v>1</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>62141</v>
+      </c>
+      <c r="C388" t="n">
+        <v>1</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>62142</v>
+      </c>
+      <c r="C389" t="n">
+        <v>1</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>62143</v>
+      </c>
+      <c r="C390" t="n">
+        <v>1</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>62144</v>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":64081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J391"/>
+  <dimension ref="A1:J471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5561,6 +5561,1046 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="B392" t="n">
+        <v>72009</v>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="n">
+        <v>72010</v>
+      </c>
+      <c r="C393" t="n">
+        <v>1</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="n">
+        <v>72011</v>
+      </c>
+      <c r="C394" t="n">
+        <v>1</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="n">
+        <v>72012</v>
+      </c>
+      <c r="C395" t="n">
+        <v>1</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="n">
+        <v>72013</v>
+      </c>
+      <c r="C396" t="n">
+        <v>1</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="n">
+        <v>72014</v>
+      </c>
+      <c r="C397" t="n">
+        <v>1</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="n">
+        <v>72015</v>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="n">
+        <v>72016</v>
+      </c>
+      <c r="C399" t="n">
+        <v>1</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="n">
+        <v>72017</v>
+      </c>
+      <c r="C400" t="n">
+        <v>1</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="n">
+        <v>72018</v>
+      </c>
+      <c r="C401" t="n">
+        <v>1</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="n">
+        <v>72028</v>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="n">
+        <v>72029</v>
+      </c>
+      <c r="C403" t="n">
+        <v>1</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="n">
+        <v>72030</v>
+      </c>
+      <c r="C404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>72031</v>
+      </c>
+      <c r="C405" t="n">
+        <v>1</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>72032</v>
+      </c>
+      <c r="C406" t="n">
+        <v>1</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>72033</v>
+      </c>
+      <c r="C407" t="n">
+        <v>1</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>72034</v>
+      </c>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>72035</v>
+      </c>
+      <c r="C409" t="n">
+        <v>1</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="n">
+        <v>72036</v>
+      </c>
+      <c r="C410" t="n">
+        <v>1</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="n">
+        <v>72037</v>
+      </c>
+      <c r="C411" t="n">
+        <v>1</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="n">
+        <v>72046</v>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="n">
+        <v>72047</v>
+      </c>
+      <c r="C413" t="n">
+        <v>1</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="n">
+        <v>72048</v>
+      </c>
+      <c r="C414" t="n">
+        <v>1</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="n">
+        <v>72049</v>
+      </c>
+      <c r="C415" t="n">
+        <v>1</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="n">
+        <v>72050</v>
+      </c>
+      <c r="C416" t="n">
+        <v>1</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="n">
+        <v>72051</v>
+      </c>
+      <c r="C417" t="n">
+        <v>1</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="n">
+        <v>72052</v>
+      </c>
+      <c r="C418" t="n">
+        <v>1</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="n">
+        <v>72053</v>
+      </c>
+      <c r="C419" t="n">
+        <v>1</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="n">
+        <v>72054</v>
+      </c>
+      <c r="C420" t="n">
+        <v>1</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="n">
+        <v>72055</v>
+      </c>
+      <c r="C421" t="n">
+        <v>1</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="n">
+        <v>72066</v>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="n">
+        <v>72067</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="n">
+        <v>72068</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="n">
+        <v>72069</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="n">
+        <v>72070</v>
+      </c>
+      <c r="C426" t="n">
+        <v>1</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="n">
+        <v>72071</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="n">
+        <v>72072</v>
+      </c>
+      <c r="C428" t="n">
+        <v>1</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="n">
+        <v>72073</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="n">
+        <v>72074</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="n">
+        <v>72075</v>
+      </c>
+      <c r="C431" t="n">
+        <v>1</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="n">
+        <v>72084</v>
+      </c>
+      <c r="C432" t="n">
+        <v>1</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="n">
+        <v>72085</v>
+      </c>
+      <c r="C433" t="n">
+        <v>1</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="n">
+        <v>72086</v>
+      </c>
+      <c r="C434" t="n">
+        <v>1</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="n">
+        <v>72087</v>
+      </c>
+      <c r="C435" t="n">
+        <v>1</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="n">
+        <v>72088</v>
+      </c>
+      <c r="C436" t="n">
+        <v>1</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="n">
+        <v>72089</v>
+      </c>
+      <c r="C437" t="n">
+        <v>1</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="n">
+        <v>72090</v>
+      </c>
+      <c r="C438" t="n">
+        <v>1</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="n">
+        <v>72091</v>
+      </c>
+      <c r="C439" t="n">
+        <v>1</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="n">
+        <v>72092</v>
+      </c>
+      <c r="C440" t="n">
+        <v>1</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" t="n">
+        <v>72093</v>
+      </c>
+      <c r="C441" t="n">
+        <v>1</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="n">
+        <v>72102</v>
+      </c>
+      <c r="C442" t="n">
+        <v>1</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="n">
+        <v>72103</v>
+      </c>
+      <c r="C443" t="n">
+        <v>1</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="n">
+        <v>72104</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" t="n">
+        <v>72105</v>
+      </c>
+      <c r="C445" t="n">
+        <v>1</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" t="n">
+        <v>72106</v>
+      </c>
+      <c r="C446" t="n">
+        <v>1</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" t="n">
+        <v>72107</v>
+      </c>
+      <c r="C447" t="n">
+        <v>1</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" t="n">
+        <v>72108</v>
+      </c>
+      <c r="C448" t="n">
+        <v>1</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" t="n">
+        <v>72109</v>
+      </c>
+      <c r="C449" t="n">
+        <v>1</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" t="n">
+        <v>72110</v>
+      </c>
+      <c r="C450" t="n">
+        <v>1</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" t="n">
+        <v>72111</v>
+      </c>
+      <c r="C451" t="n">
+        <v>1</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" t="n">
+        <v>72120</v>
+      </c>
+      <c r="C452" t="n">
+        <v>1</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" t="n">
+        <v>72121</v>
+      </c>
+      <c r="C453" t="n">
+        <v>1</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" t="n">
+        <v>72122</v>
+      </c>
+      <c r="C454" t="n">
+        <v>1</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" t="n">
+        <v>72123</v>
+      </c>
+      <c r="C455" t="n">
+        <v>1</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="n">
+        <v>72124</v>
+      </c>
+      <c r="C456" t="n">
+        <v>1</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" t="n">
+        <v>72125</v>
+      </c>
+      <c r="C457" t="n">
+        <v>1</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="n">
+        <v>72126</v>
+      </c>
+      <c r="C458" t="n">
+        <v>1</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" t="n">
+        <v>72127</v>
+      </c>
+      <c r="C459" t="n">
+        <v>1</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" t="n">
+        <v>72128</v>
+      </c>
+      <c r="C460" t="n">
+        <v>1</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" t="n">
+        <v>72129</v>
+      </c>
+      <c r="C461" t="n">
+        <v>1</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" t="n">
+        <v>72138</v>
+      </c>
+      <c r="C462" t="n">
+        <v>1</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" t="n">
+        <v>72139</v>
+      </c>
+      <c r="C463" t="n">
+        <v>1</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" t="n">
+        <v>72140</v>
+      </c>
+      <c r="C464" t="n">
+        <v>1</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" t="n">
+        <v>72141</v>
+      </c>
+      <c r="C465" t="n">
+        <v>1</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" t="n">
+        <v>72142</v>
+      </c>
+      <c r="C466" t="n">
+        <v>1</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" t="n">
+        <v>72143</v>
+      </c>
+      <c r="C467" t="n">
+        <v>1</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" t="n">
+        <v>72144</v>
+      </c>
+      <c r="C468" t="n">
+        <v>1</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" t="n">
+        <v>72145</v>
+      </c>
+      <c r="C469" t="n">
+        <v>1</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" t="n">
+        <v>72146</v>
+      </c>
+      <c r="C470" t="n">
+        <v>1</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" t="n">
+        <v>72147</v>
+      </c>
+      <c r="C471" t="n">
+        <v>1</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":74081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J471"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6601,6 +6601,1046 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="B472" t="n">
+        <v>82009</v>
+      </c>
+      <c r="C472" t="n">
+        <v>1</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" t="n">
+        <v>82010</v>
+      </c>
+      <c r="C473" t="n">
+        <v>1</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" t="n">
+        <v>82011</v>
+      </c>
+      <c r="C474" t="n">
+        <v>1</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" t="n">
+        <v>82012</v>
+      </c>
+      <c r="C475" t="n">
+        <v>1</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" t="n">
+        <v>82013</v>
+      </c>
+      <c r="C476" t="n">
+        <v>1</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" t="n">
+        <v>82014</v>
+      </c>
+      <c r="C477" t="n">
+        <v>1</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" t="n">
+        <v>82015</v>
+      </c>
+      <c r="C478" t="n">
+        <v>1</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" t="n">
+        <v>82016</v>
+      </c>
+      <c r="C479" t="n">
+        <v>1</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" t="n">
+        <v>82017</v>
+      </c>
+      <c r="C480" t="n">
+        <v>1</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" t="n">
+        <v>82018</v>
+      </c>
+      <c r="C481" t="n">
+        <v>1</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" t="n">
+        <v>82027</v>
+      </c>
+      <c r="C482" t="n">
+        <v>1</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" t="n">
+        <v>82028</v>
+      </c>
+      <c r="C483" t="n">
+        <v>1</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" t="n">
+        <v>82029</v>
+      </c>
+      <c r="C484" t="n">
+        <v>1</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" t="n">
+        <v>82030</v>
+      </c>
+      <c r="C485" t="n">
+        <v>1</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" t="n">
+        <v>82031</v>
+      </c>
+      <c r="C486" t="n">
+        <v>1</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" t="n">
+        <v>82032</v>
+      </c>
+      <c r="C487" t="n">
+        <v>1</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" t="n">
+        <v>82033</v>
+      </c>
+      <c r="C488" t="n">
+        <v>1</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" t="n">
+        <v>82034</v>
+      </c>
+      <c r="C489" t="n">
+        <v>1</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" t="n">
+        <v>82035</v>
+      </c>
+      <c r="C490" t="n">
+        <v>1</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" t="n">
+        <v>82036</v>
+      </c>
+      <c r="C491" t="n">
+        <v>1</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" t="n">
+        <v>82045</v>
+      </c>
+      <c r="C492" t="n">
+        <v>1</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" t="n">
+        <v>82046</v>
+      </c>
+      <c r="C493" t="n">
+        <v>1</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" t="n">
+        <v>82047</v>
+      </c>
+      <c r="C494" t="n">
+        <v>1</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" t="n">
+        <v>82048</v>
+      </c>
+      <c r="C495" t="n">
+        <v>1</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" t="n">
+        <v>82049</v>
+      </c>
+      <c r="C496" t="n">
+        <v>1</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" t="n">
+        <v>82050</v>
+      </c>
+      <c r="C497" t="n">
+        <v>1</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" t="n">
+        <v>82051</v>
+      </c>
+      <c r="C498" t="n">
+        <v>1</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" t="n">
+        <v>82052</v>
+      </c>
+      <c r="C499" t="n">
+        <v>1</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" t="n">
+        <v>82053</v>
+      </c>
+      <c r="C500" t="n">
+        <v>1</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" t="n">
+        <v>82054</v>
+      </c>
+      <c r="C501" t="n">
+        <v>1</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" t="n">
+        <v>82063</v>
+      </c>
+      <c r="C502" t="n">
+        <v>1</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" t="n">
+        <v>82064</v>
+      </c>
+      <c r="C503" t="n">
+        <v>1</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" t="n">
+        <v>82065</v>
+      </c>
+      <c r="C504" t="n">
+        <v>1</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" t="n">
+        <v>82066</v>
+      </c>
+      <c r="C505" t="n">
+        <v>1</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" t="n">
+        <v>82067</v>
+      </c>
+      <c r="C506" t="n">
+        <v>1</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" t="n">
+        <v>82068</v>
+      </c>
+      <c r="C507" t="n">
+        <v>1</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" t="n">
+        <v>82069</v>
+      </c>
+      <c r="C508" t="n">
+        <v>1</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" t="n">
+        <v>82070</v>
+      </c>
+      <c r="C509" t="n">
+        <v>1</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" t="n">
+        <v>82071</v>
+      </c>
+      <c r="C510" t="n">
+        <v>1</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" t="n">
+        <v>82072</v>
+      </c>
+      <c r="C511" t="n">
+        <v>1</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" t="n">
+        <v>82081</v>
+      </c>
+      <c r="C512" t="n">
+        <v>1</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" t="n">
+        <v>82082</v>
+      </c>
+      <c r="C513" t="n">
+        <v>1</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" t="n">
+        <v>82083</v>
+      </c>
+      <c r="C514" t="n">
+        <v>1</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" t="n">
+        <v>82084</v>
+      </c>
+      <c r="C515" t="n">
+        <v>1</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" t="n">
+        <v>82085</v>
+      </c>
+      <c r="C516" t="n">
+        <v>1</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" t="n">
+        <v>82086</v>
+      </c>
+      <c r="C517" t="n">
+        <v>1</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" t="n">
+        <v>82087</v>
+      </c>
+      <c r="C518" t="n">
+        <v>1</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" t="n">
+        <v>82088</v>
+      </c>
+      <c r="C519" t="n">
+        <v>1</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" t="n">
+        <v>82089</v>
+      </c>
+      <c r="C520" t="n">
+        <v>1</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" t="n">
+        <v>82090</v>
+      </c>
+      <c r="C521" t="n">
+        <v>1</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" t="n">
+        <v>82099</v>
+      </c>
+      <c r="C522" t="n">
+        <v>1</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" t="n">
+        <v>82100</v>
+      </c>
+      <c r="C523" t="n">
+        <v>1</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" t="n">
+        <v>82101</v>
+      </c>
+      <c r="C524" t="n">
+        <v>1</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" t="n">
+        <v>82102</v>
+      </c>
+      <c r="C525" t="n">
+        <v>1</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" t="n">
+        <v>82103</v>
+      </c>
+      <c r="C526" t="n">
+        <v>1</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" t="n">
+        <v>82104</v>
+      </c>
+      <c r="C527" t="n">
+        <v>1</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" t="n">
+        <v>82105</v>
+      </c>
+      <c r="C528" t="n">
+        <v>1</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" t="n">
+        <v>82106</v>
+      </c>
+      <c r="C529" t="n">
+        <v>1</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" t="n">
+        <v>82107</v>
+      </c>
+      <c r="C530" t="n">
+        <v>1</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" t="n">
+        <v>82108</v>
+      </c>
+      <c r="C531" t="n">
+        <v>1</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" t="n">
+        <v>82117</v>
+      </c>
+      <c r="C532" t="n">
+        <v>1</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" t="n">
+        <v>82118</v>
+      </c>
+      <c r="C533" t="n">
+        <v>1</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" t="n">
+        <v>82119</v>
+      </c>
+      <c r="C534" t="n">
+        <v>1</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" t="n">
+        <v>82120</v>
+      </c>
+      <c r="C535" t="n">
+        <v>1</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" t="n">
+        <v>82121</v>
+      </c>
+      <c r="C536" t="n">
+        <v>1</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" t="n">
+        <v>82122</v>
+      </c>
+      <c r="C537" t="n">
+        <v>1</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" t="n">
+        <v>82123</v>
+      </c>
+      <c r="C538" t="n">
+        <v>1</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" t="n">
+        <v>82124</v>
+      </c>
+      <c r="C539" t="n">
+        <v>1</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" t="n">
+        <v>82125</v>
+      </c>
+      <c r="C540" t="n">
+        <v>1</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" t="n">
+        <v>82126</v>
+      </c>
+      <c r="C541" t="n">
+        <v>1</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" t="n">
+        <v>82135</v>
+      </c>
+      <c r="C542" t="n">
+        <v>1</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" t="n">
+        <v>82136</v>
+      </c>
+      <c r="C543" t="n">
+        <v>1</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" t="n">
+        <v>82137</v>
+      </c>
+      <c r="C544" t="n">
+        <v>1</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" t="n">
+        <v>82138</v>
+      </c>
+      <c r="C545" t="n">
+        <v>1</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" t="n">
+        <v>82139</v>
+      </c>
+      <c r="C546" t="n">
+        <v>1</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" t="n">
+        <v>82140</v>
+      </c>
+      <c r="C547" t="n">
+        <v>1</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" t="n">
+        <v>82141</v>
+      </c>
+      <c r="C548" t="n">
+        <v>1</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" t="n">
+        <v>82142</v>
+      </c>
+      <c r="C549" t="n">
+        <v>1</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" t="n">
+        <v>82143</v>
+      </c>
+      <c r="C550" t="n">
+        <v>1</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" t="n">
+        <v>82144</v>
+      </c>
+      <c r="C551" t="n">
+        <v>1</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":84081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J551"/>
+  <dimension ref="A1:J631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7641,6 +7641,1046 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="B552" t="n">
+        <v>92009</v>
+      </c>
+      <c r="C552" t="n">
+        <v>1</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" t="n">
+        <v>92010</v>
+      </c>
+      <c r="C553" t="n">
+        <v>1</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" t="n">
+        <v>92011</v>
+      </c>
+      <c r="C554" t="n">
+        <v>1</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" t="n">
+        <v>92012</v>
+      </c>
+      <c r="C555" t="n">
+        <v>1</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" t="n">
+        <v>92013</v>
+      </c>
+      <c r="C556" t="n">
+        <v>1</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" t="n">
+        <v>92014</v>
+      </c>
+      <c r="C557" t="n">
+        <v>1</v>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" t="n">
+        <v>92015</v>
+      </c>
+      <c r="C558" t="n">
+        <v>1</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" t="n">
+        <v>92016</v>
+      </c>
+      <c r="C559" t="n">
+        <v>1</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" t="n">
+        <v>92017</v>
+      </c>
+      <c r="C560" t="n">
+        <v>1</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" t="n">
+        <v>92018</v>
+      </c>
+      <c r="C561" t="n">
+        <v>1</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" t="n">
+        <v>92027</v>
+      </c>
+      <c r="C562" t="n">
+        <v>1</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" t="n">
+        <v>92028</v>
+      </c>
+      <c r="C563" t="n">
+        <v>1</v>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" t="n">
+        <v>92029</v>
+      </c>
+      <c r="C564" t="n">
+        <v>1</v>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C565" t="n">
+        <v>1</v>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" t="n">
+        <v>92031</v>
+      </c>
+      <c r="C566" t="n">
+        <v>1</v>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" t="n">
+        <v>92032</v>
+      </c>
+      <c r="C567" t="n">
+        <v>1</v>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" t="n">
+        <v>92033</v>
+      </c>
+      <c r="C568" t="n">
+        <v>1</v>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" t="n">
+        <v>92034</v>
+      </c>
+      <c r="C569" t="n">
+        <v>1</v>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" t="n">
+        <v>92035</v>
+      </c>
+      <c r="C570" t="n">
+        <v>1</v>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" t="n">
+        <v>92036</v>
+      </c>
+      <c r="C571" t="n">
+        <v>1</v>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" t="n">
+        <v>92045</v>
+      </c>
+      <c r="C572" t="n">
+        <v>1</v>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" t="n">
+        <v>92046</v>
+      </c>
+      <c r="C573" t="n">
+        <v>1</v>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" t="n">
+        <v>92047</v>
+      </c>
+      <c r="C574" t="n">
+        <v>1</v>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" t="n">
+        <v>92048</v>
+      </c>
+      <c r="C575" t="n">
+        <v>1</v>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="B576" t="n">
+        <v>92049</v>
+      </c>
+      <c r="C576" t="n">
+        <v>1</v>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" t="n">
+        <v>92050</v>
+      </c>
+      <c r="C577" t="n">
+        <v>1</v>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" t="n">
+        <v>92051</v>
+      </c>
+      <c r="C578" t="n">
+        <v>1</v>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" t="n">
+        <v>92052</v>
+      </c>
+      <c r="C579" t="n">
+        <v>1</v>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" t="n">
+        <v>92053</v>
+      </c>
+      <c r="C580" t="n">
+        <v>1</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" t="n">
+        <v>92054</v>
+      </c>
+      <c r="C581" t="n">
+        <v>1</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" t="n">
+        <v>92063</v>
+      </c>
+      <c r="C582" t="n">
+        <v>1</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" t="n">
+        <v>92064</v>
+      </c>
+      <c r="C583" t="n">
+        <v>1</v>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" t="n">
+        <v>92065</v>
+      </c>
+      <c r="C584" t="n">
+        <v>1</v>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" t="n">
+        <v>92066</v>
+      </c>
+      <c r="C585" t="n">
+        <v>1</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="B586" t="n">
+        <v>92067</v>
+      </c>
+      <c r="C586" t="n">
+        <v>1</v>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" t="n">
+        <v>92068</v>
+      </c>
+      <c r="C587" t="n">
+        <v>1</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" t="n">
+        <v>92069</v>
+      </c>
+      <c r="C588" t="n">
+        <v>1</v>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" t="n">
+        <v>92070</v>
+      </c>
+      <c r="C589" t="n">
+        <v>1</v>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" t="n">
+        <v>92071</v>
+      </c>
+      <c r="C590" t="n">
+        <v>1</v>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" t="n">
+        <v>92072</v>
+      </c>
+      <c r="C591" t="n">
+        <v>1</v>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" t="n">
+        <v>92081</v>
+      </c>
+      <c r="C592" t="n">
+        <v>1</v>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" t="n">
+        <v>92082</v>
+      </c>
+      <c r="C593" t="n">
+        <v>1</v>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" t="n">
+        <v>92083</v>
+      </c>
+      <c r="C594" t="n">
+        <v>1</v>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" t="n">
+        <v>92084</v>
+      </c>
+      <c r="C595" t="n">
+        <v>1</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" t="n">
+        <v>92085</v>
+      </c>
+      <c r="C596" t="n">
+        <v>1</v>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" t="n">
+        <v>92086</v>
+      </c>
+      <c r="C597" t="n">
+        <v>1</v>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" t="n">
+        <v>92087</v>
+      </c>
+      <c r="C598" t="n">
+        <v>1</v>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" t="n">
+        <v>92088</v>
+      </c>
+      <c r="C599" t="n">
+        <v>1</v>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" t="n">
+        <v>92089</v>
+      </c>
+      <c r="C600" t="n">
+        <v>1</v>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" t="n">
+        <v>92090</v>
+      </c>
+      <c r="C601" t="n">
+        <v>1</v>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" t="n">
+        <v>92099</v>
+      </c>
+      <c r="C602" t="n">
+        <v>1</v>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" t="n">
+        <v>92100</v>
+      </c>
+      <c r="C603" t="n">
+        <v>1</v>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" t="n">
+        <v>92101</v>
+      </c>
+      <c r="C604" t="n">
+        <v>1</v>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" t="n">
+        <v>92102</v>
+      </c>
+      <c r="C605" t="n">
+        <v>1</v>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" t="n">
+        <v>92103</v>
+      </c>
+      <c r="C606" t="n">
+        <v>1</v>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" t="n">
+        <v>92104</v>
+      </c>
+      <c r="C607" t="n">
+        <v>1</v>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" t="n">
+        <v>92105</v>
+      </c>
+      <c r="C608" t="n">
+        <v>1</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" t="n">
+        <v>92106</v>
+      </c>
+      <c r="C609" t="n">
+        <v>1</v>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" t="n">
+        <v>92107</v>
+      </c>
+      <c r="C610" t="n">
+        <v>1</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" t="n">
+        <v>92108</v>
+      </c>
+      <c r="C611" t="n">
+        <v>1</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" t="n">
+        <v>92117</v>
+      </c>
+      <c r="C612" t="n">
+        <v>1</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" t="n">
+        <v>92118</v>
+      </c>
+      <c r="C613" t="n">
+        <v>1</v>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" t="n">
+        <v>92119</v>
+      </c>
+      <c r="C614" t="n">
+        <v>1</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" t="n">
+        <v>92120</v>
+      </c>
+      <c r="C615" t="n">
+        <v>1</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" t="n">
+        <v>92121</v>
+      </c>
+      <c r="C616" t="n">
+        <v>1</v>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" t="n">
+        <v>92122</v>
+      </c>
+      <c r="C617" t="n">
+        <v>1</v>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" t="n">
+        <v>92123</v>
+      </c>
+      <c r="C618" t="n">
+        <v>1</v>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" t="n">
+        <v>92124</v>
+      </c>
+      <c r="C619" t="n">
+        <v>1</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" t="n">
+        <v>92125</v>
+      </c>
+      <c r="C620" t="n">
+        <v>1</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" t="n">
+        <v>92126</v>
+      </c>
+      <c r="C621" t="n">
+        <v>1</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" t="n">
+        <v>92135</v>
+      </c>
+      <c r="C622" t="n">
+        <v>1</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" t="n">
+        <v>92136</v>
+      </c>
+      <c r="C623" t="n">
+        <v>1</v>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" t="n">
+        <v>92137</v>
+      </c>
+      <c r="C624" t="n">
+        <v>1</v>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" t="n">
+        <v>92138</v>
+      </c>
+      <c r="C625" t="n">
+        <v>1</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" t="n">
+        <v>92139</v>
+      </c>
+      <c r="C626" t="n">
+        <v>1</v>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" t="n">
+        <v>92140</v>
+      </c>
+      <c r="C627" t="n">
+        <v>1</v>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" t="n">
+        <v>92141</v>
+      </c>
+      <c r="C628" t="n">
+        <v>1</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" t="n">
+        <v>92142</v>
+      </c>
+      <c r="C629" t="n">
+        <v>1</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" t="n">
+        <v>92143</v>
+      </c>
+      <c r="C630" t="n">
+        <v>1</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" t="n">
+        <v>92144</v>
+      </c>
+      <c r="C631" t="n">
+        <v>1</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":94081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J631"/>
+  <dimension ref="A1:J716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8681,6 +8681,1111 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="B632" t="n">
+        <v>102009</v>
+      </c>
+      <c r="C632" t="n">
+        <v>1</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" t="n">
+        <v>102010</v>
+      </c>
+      <c r="C633" t="n">
+        <v>1</v>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" t="n">
+        <v>102011</v>
+      </c>
+      <c r="C634" t="n">
+        <v>1</v>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" t="n">
+        <v>102012</v>
+      </c>
+      <c r="C635" t="n">
+        <v>1</v>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" t="n">
+        <v>102013</v>
+      </c>
+      <c r="C636" t="n">
+        <v>1</v>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" t="n">
+        <v>102014</v>
+      </c>
+      <c r="C637" t="n">
+        <v>1</v>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" t="n">
+        <v>102015</v>
+      </c>
+      <c r="C638" t="n">
+        <v>1</v>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" t="n">
+        <v>102016</v>
+      </c>
+      <c r="C639" t="n">
+        <v>1</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" t="n">
+        <v>102017</v>
+      </c>
+      <c r="C640" t="n">
+        <v>1</v>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" t="n">
+        <v>102018</v>
+      </c>
+      <c r="C641" t="n">
+        <v>1</v>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" t="n">
+        <v>102019</v>
+      </c>
+      <c r="C642" t="n">
+        <v>1</v>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":100011,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" t="n">
+        <v>102019</v>
+      </c>
+      <c r="C643" t="n">
+        <v>2</v>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":100012,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" t="n">
+        <v>102020</v>
+      </c>
+      <c r="C644" t="n">
+        <v>1</v>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":100013,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" t="n">
+        <v>102021</v>
+      </c>
+      <c r="C645" t="n">
+        <v>1</v>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":100010,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" t="n">
+        <v>102022</v>
+      </c>
+      <c r="C646" t="n">
+        <v>1</v>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>{"type":"AdjustAbilityLevel","ability_id":100009,"bonus":1,"cap_delta":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" t="n">
+        <v>102027</v>
+      </c>
+      <c r="C647" t="n">
+        <v>1</v>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" t="n">
+        <v>102028</v>
+      </c>
+      <c r="C648" t="n">
+        <v>1</v>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" t="n">
+        <v>102029</v>
+      </c>
+      <c r="C649" t="n">
+        <v>1</v>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" t="n">
+        <v>102030</v>
+      </c>
+      <c r="C650" t="n">
+        <v>1</v>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" t="n">
+        <v>102031</v>
+      </c>
+      <c r="C651" t="n">
+        <v>1</v>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" t="n">
+        <v>102032</v>
+      </c>
+      <c r="C652" t="n">
+        <v>1</v>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" t="n">
+        <v>102033</v>
+      </c>
+      <c r="C653" t="n">
+        <v>1</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" t="n">
+        <v>102034</v>
+      </c>
+      <c r="C654" t="n">
+        <v>1</v>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" t="n">
+        <v>102035</v>
+      </c>
+      <c r="C655" t="n">
+        <v>1</v>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" t="n">
+        <v>102036</v>
+      </c>
+      <c r="C656" t="n">
+        <v>1</v>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" t="n">
+        <v>102045</v>
+      </c>
+      <c r="C657" t="n">
+        <v>1</v>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" t="n">
+        <v>102046</v>
+      </c>
+      <c r="C658" t="n">
+        <v>1</v>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" t="n">
+        <v>102047</v>
+      </c>
+      <c r="C659" t="n">
+        <v>1</v>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" t="n">
+        <v>102048</v>
+      </c>
+      <c r="C660" t="n">
+        <v>1</v>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="B661" t="n">
+        <v>102049</v>
+      </c>
+      <c r="C661" t="n">
+        <v>1</v>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="B662" t="n">
+        <v>102050</v>
+      </c>
+      <c r="C662" t="n">
+        <v>1</v>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="B663" t="n">
+        <v>102051</v>
+      </c>
+      <c r="C663" t="n">
+        <v>1</v>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="B664" t="n">
+        <v>102052</v>
+      </c>
+      <c r="C664" t="n">
+        <v>1</v>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="B665" t="n">
+        <v>102053</v>
+      </c>
+      <c r="C665" t="n">
+        <v>1</v>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="B666" t="n">
+        <v>102054</v>
+      </c>
+      <c r="C666" t="n">
+        <v>1</v>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="B667" t="n">
+        <v>102064</v>
+      </c>
+      <c r="C667" t="n">
+        <v>1</v>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="B668" t="n">
+        <v>102065</v>
+      </c>
+      <c r="C668" t="n">
+        <v>1</v>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="B669" t="n">
+        <v>102066</v>
+      </c>
+      <c r="C669" t="n">
+        <v>1</v>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="B670" t="n">
+        <v>102067</v>
+      </c>
+      <c r="C670" t="n">
+        <v>1</v>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="B671" t="n">
+        <v>102068</v>
+      </c>
+      <c r="C671" t="n">
+        <v>1</v>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="B672" t="n">
+        <v>102069</v>
+      </c>
+      <c r="C672" t="n">
+        <v>1</v>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="B673" t="n">
+        <v>102070</v>
+      </c>
+      <c r="C673" t="n">
+        <v>1</v>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="B674" t="n">
+        <v>102071</v>
+      </c>
+      <c r="C674" t="n">
+        <v>1</v>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="B675" t="n">
+        <v>102072</v>
+      </c>
+      <c r="C675" t="n">
+        <v>1</v>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="B676" t="n">
+        <v>102073</v>
+      </c>
+      <c r="C676" t="n">
+        <v>1</v>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="B677" t="n">
+        <v>102082</v>
+      </c>
+      <c r="C677" t="n">
+        <v>1</v>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="B678" t="n">
+        <v>102083</v>
+      </c>
+      <c r="C678" t="n">
+        <v>1</v>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="B679" t="n">
+        <v>102084</v>
+      </c>
+      <c r="C679" t="n">
+        <v>1</v>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="B680" t="n">
+        <v>102085</v>
+      </c>
+      <c r="C680" t="n">
+        <v>1</v>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="B681" t="n">
+        <v>102086</v>
+      </c>
+      <c r="C681" t="n">
+        <v>1</v>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="B682" t="n">
+        <v>102087</v>
+      </c>
+      <c r="C682" t="n">
+        <v>1</v>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="B683" t="n">
+        <v>102088</v>
+      </c>
+      <c r="C683" t="n">
+        <v>1</v>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="B684" t="n">
+        <v>102089</v>
+      </c>
+      <c r="C684" t="n">
+        <v>1</v>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="B685" t="n">
+        <v>102090</v>
+      </c>
+      <c r="C685" t="n">
+        <v>1</v>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="B686" t="n">
+        <v>102091</v>
+      </c>
+      <c r="C686" t="n">
+        <v>1</v>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="B687" t="n">
+        <v>102101</v>
+      </c>
+      <c r="C687" t="n">
+        <v>1</v>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="B688" t="n">
+        <v>102102</v>
+      </c>
+      <c r="C688" t="n">
+        <v>1</v>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="B689" t="n">
+        <v>102103</v>
+      </c>
+      <c r="C689" t="n">
+        <v>1</v>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="B690" t="n">
+        <v>102104</v>
+      </c>
+      <c r="C690" t="n">
+        <v>1</v>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="B691" t="n">
+        <v>102105</v>
+      </c>
+      <c r="C691" t="n">
+        <v>1</v>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="B692" t="n">
+        <v>102106</v>
+      </c>
+      <c r="C692" t="n">
+        <v>1</v>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="B693" t="n">
+        <v>102107</v>
+      </c>
+      <c r="C693" t="n">
+        <v>1</v>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="B694" t="n">
+        <v>102108</v>
+      </c>
+      <c r="C694" t="n">
+        <v>1</v>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="B695" t="n">
+        <v>102109</v>
+      </c>
+      <c r="C695" t="n">
+        <v>1</v>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="B696" t="n">
+        <v>102110</v>
+      </c>
+      <c r="C696" t="n">
+        <v>1</v>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="B697" t="n">
+        <v>102119</v>
+      </c>
+      <c r="C697" t="n">
+        <v>1</v>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="B698" t="n">
+        <v>102120</v>
+      </c>
+      <c r="C698" t="n">
+        <v>1</v>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="B699" t="n">
+        <v>102121</v>
+      </c>
+      <c r="C699" t="n">
+        <v>1</v>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="B700" t="n">
+        <v>102122</v>
+      </c>
+      <c r="C700" t="n">
+        <v>1</v>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="B701" t="n">
+        <v>102123</v>
+      </c>
+      <c r="C701" t="n">
+        <v>1</v>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="B702" t="n">
+        <v>102124</v>
+      </c>
+      <c r="C702" t="n">
+        <v>1</v>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="B703" t="n">
+        <v>102125</v>
+      </c>
+      <c r="C703" t="n">
+        <v>1</v>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="B704" t="n">
+        <v>102126</v>
+      </c>
+      <c r="C704" t="n">
+        <v>1</v>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="B705" t="n">
+        <v>102127</v>
+      </c>
+      <c r="C705" t="n">
+        <v>1</v>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="B706" t="n">
+        <v>102128</v>
+      </c>
+      <c r="C706" t="n">
+        <v>1</v>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="B707" t="n">
+        <v>102137</v>
+      </c>
+      <c r="C707" t="n">
+        <v>1</v>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="B708" t="n">
+        <v>102138</v>
+      </c>
+      <c r="C708" t="n">
+        <v>1</v>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="B709" t="n">
+        <v>102139</v>
+      </c>
+      <c r="C709" t="n">
+        <v>1</v>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="B710" t="n">
+        <v>102140</v>
+      </c>
+      <c r="C710" t="n">
+        <v>1</v>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="B711" t="n">
+        <v>102141</v>
+      </c>
+      <c r="C711" t="n">
+        <v>1</v>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="B712" t="n">
+        <v>102142</v>
+      </c>
+      <c r="C712" t="n">
+        <v>1</v>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="B713" t="n">
+        <v>102143</v>
+      </c>
+      <c r="C713" t="n">
+        <v>1</v>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="B714" t="n">
+        <v>102144</v>
+      </c>
+      <c r="C714" t="n">
+        <v>1</v>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="B715" t="n">
+        <v>102145</v>
+      </c>
+      <c r="C715" t="n">
+        <v>1</v>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="B716" t="n">
+        <v>102146</v>
+      </c>
+      <c r="C716" t="n">
+        <v>1</v>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":104081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J716"/>
+  <dimension ref="A1:J796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9786,6 +9786,1046 @@
         </is>
       </c>
     </row>
+    <row r="717">
+      <c r="B717" t="n">
+        <v>112009</v>
+      </c>
+      <c r="C717" t="n">
+        <v>1</v>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="B718" t="n">
+        <v>112010</v>
+      </c>
+      <c r="C718" t="n">
+        <v>1</v>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="B719" t="n">
+        <v>112011</v>
+      </c>
+      <c r="C719" t="n">
+        <v>1</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="B720" t="n">
+        <v>112012</v>
+      </c>
+      <c r="C720" t="n">
+        <v>1</v>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="B721" t="n">
+        <v>112013</v>
+      </c>
+      <c r="C721" t="n">
+        <v>1</v>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="B722" t="n">
+        <v>112014</v>
+      </c>
+      <c r="C722" t="n">
+        <v>1</v>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="B723" t="n">
+        <v>112015</v>
+      </c>
+      <c r="C723" t="n">
+        <v>1</v>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="B724" t="n">
+        <v>112016</v>
+      </c>
+      <c r="C724" t="n">
+        <v>1</v>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="B725" t="n">
+        <v>112017</v>
+      </c>
+      <c r="C725" t="n">
+        <v>1</v>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="B726" t="n">
+        <v>112018</v>
+      </c>
+      <c r="C726" t="n">
+        <v>1</v>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="B727" t="n">
+        <v>112027</v>
+      </c>
+      <c r="C727" t="n">
+        <v>1</v>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="B728" t="n">
+        <v>112028</v>
+      </c>
+      <c r="C728" t="n">
+        <v>1</v>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="B729" t="n">
+        <v>112029</v>
+      </c>
+      <c r="C729" t="n">
+        <v>1</v>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="B730" t="n">
+        <v>112030</v>
+      </c>
+      <c r="C730" t="n">
+        <v>1</v>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="B731" t="n">
+        <v>112031</v>
+      </c>
+      <c r="C731" t="n">
+        <v>1</v>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="B732" t="n">
+        <v>112032</v>
+      </c>
+      <c r="C732" t="n">
+        <v>1</v>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="B733" t="n">
+        <v>112033</v>
+      </c>
+      <c r="C733" t="n">
+        <v>1</v>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="B734" t="n">
+        <v>112034</v>
+      </c>
+      <c r="C734" t="n">
+        <v>1</v>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="B735" t="n">
+        <v>112035</v>
+      </c>
+      <c r="C735" t="n">
+        <v>1</v>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="B736" t="n">
+        <v>112036</v>
+      </c>
+      <c r="C736" t="n">
+        <v>1</v>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="B737" t="n">
+        <v>112045</v>
+      </c>
+      <c r="C737" t="n">
+        <v>1</v>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="B738" t="n">
+        <v>112046</v>
+      </c>
+      <c r="C738" t="n">
+        <v>1</v>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="B739" t="n">
+        <v>112047</v>
+      </c>
+      <c r="C739" t="n">
+        <v>1</v>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="B740" t="n">
+        <v>112048</v>
+      </c>
+      <c r="C740" t="n">
+        <v>1</v>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="B741" t="n">
+        <v>112049</v>
+      </c>
+      <c r="C741" t="n">
+        <v>1</v>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="B742" t="n">
+        <v>112050</v>
+      </c>
+      <c r="C742" t="n">
+        <v>1</v>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="B743" t="n">
+        <v>112051</v>
+      </c>
+      <c r="C743" t="n">
+        <v>1</v>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="B744" t="n">
+        <v>112052</v>
+      </c>
+      <c r="C744" t="n">
+        <v>1</v>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="B745" t="n">
+        <v>112053</v>
+      </c>
+      <c r="C745" t="n">
+        <v>1</v>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="B746" t="n">
+        <v>112054</v>
+      </c>
+      <c r="C746" t="n">
+        <v>1</v>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="B747" t="n">
+        <v>112063</v>
+      </c>
+      <c r="C747" t="n">
+        <v>1</v>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="B748" t="n">
+        <v>112064</v>
+      </c>
+      <c r="C748" t="n">
+        <v>1</v>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="B749" t="n">
+        <v>112065</v>
+      </c>
+      <c r="C749" t="n">
+        <v>1</v>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="B750" t="n">
+        <v>112066</v>
+      </c>
+      <c r="C750" t="n">
+        <v>1</v>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="B751" t="n">
+        <v>112067</v>
+      </c>
+      <c r="C751" t="n">
+        <v>1</v>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="B752" t="n">
+        <v>112068</v>
+      </c>
+      <c r="C752" t="n">
+        <v>1</v>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="B753" t="n">
+        <v>112069</v>
+      </c>
+      <c r="C753" t="n">
+        <v>1</v>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="B754" t="n">
+        <v>112070</v>
+      </c>
+      <c r="C754" t="n">
+        <v>1</v>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="B755" t="n">
+        <v>112071</v>
+      </c>
+      <c r="C755" t="n">
+        <v>1</v>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="B756" t="n">
+        <v>112072</v>
+      </c>
+      <c r="C756" t="n">
+        <v>1</v>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="B757" t="n">
+        <v>112081</v>
+      </c>
+      <c r="C757" t="n">
+        <v>1</v>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="B758" t="n">
+        <v>112082</v>
+      </c>
+      <c r="C758" t="n">
+        <v>1</v>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="B759" t="n">
+        <v>112083</v>
+      </c>
+      <c r="C759" t="n">
+        <v>1</v>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="B760" t="n">
+        <v>112084</v>
+      </c>
+      <c r="C760" t="n">
+        <v>1</v>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="B761" t="n">
+        <v>112085</v>
+      </c>
+      <c r="C761" t="n">
+        <v>1</v>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="B762" t="n">
+        <v>112086</v>
+      </c>
+      <c r="C762" t="n">
+        <v>1</v>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="B763" t="n">
+        <v>112087</v>
+      </c>
+      <c r="C763" t="n">
+        <v>1</v>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="B764" t="n">
+        <v>112088</v>
+      </c>
+      <c r="C764" t="n">
+        <v>1</v>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="B765" t="n">
+        <v>112089</v>
+      </c>
+      <c r="C765" t="n">
+        <v>1</v>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="B766" t="n">
+        <v>112090</v>
+      </c>
+      <c r="C766" t="n">
+        <v>1</v>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="B767" t="n">
+        <v>112099</v>
+      </c>
+      <c r="C767" t="n">
+        <v>1</v>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="B768" t="n">
+        <v>112100</v>
+      </c>
+      <c r="C768" t="n">
+        <v>1</v>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="B769" t="n">
+        <v>112101</v>
+      </c>
+      <c r="C769" t="n">
+        <v>1</v>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="B770" t="n">
+        <v>112102</v>
+      </c>
+      <c r="C770" t="n">
+        <v>1</v>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="B771" t="n">
+        <v>112103</v>
+      </c>
+      <c r="C771" t="n">
+        <v>1</v>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="B772" t="n">
+        <v>112104</v>
+      </c>
+      <c r="C772" t="n">
+        <v>1</v>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="B773" t="n">
+        <v>112105</v>
+      </c>
+      <c r="C773" t="n">
+        <v>1</v>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="B774" t="n">
+        <v>112106</v>
+      </c>
+      <c r="C774" t="n">
+        <v>1</v>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="B775" t="n">
+        <v>112107</v>
+      </c>
+      <c r="C775" t="n">
+        <v>1</v>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="B776" t="n">
+        <v>112108</v>
+      </c>
+      <c r="C776" t="n">
+        <v>1</v>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="B777" t="n">
+        <v>112119</v>
+      </c>
+      <c r="C777" t="n">
+        <v>1</v>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="B778" t="n">
+        <v>112120</v>
+      </c>
+      <c r="C778" t="n">
+        <v>1</v>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="B779" t="n">
+        <v>112121</v>
+      </c>
+      <c r="C779" t="n">
+        <v>1</v>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="B780" t="n">
+        <v>112122</v>
+      </c>
+      <c r="C780" t="n">
+        <v>1</v>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="B781" t="n">
+        <v>112123</v>
+      </c>
+      <c r="C781" t="n">
+        <v>1</v>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="B782" t="n">
+        <v>112124</v>
+      </c>
+      <c r="C782" t="n">
+        <v>1</v>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="B783" t="n">
+        <v>112125</v>
+      </c>
+      <c r="C783" t="n">
+        <v>1</v>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="B784" t="n">
+        <v>112126</v>
+      </c>
+      <c r="C784" t="n">
+        <v>1</v>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="B785" t="n">
+        <v>112127</v>
+      </c>
+      <c r="C785" t="n">
+        <v>1</v>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="B786" t="n">
+        <v>112128</v>
+      </c>
+      <c r="C786" t="n">
+        <v>1</v>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="B787" t="n">
+        <v>112137</v>
+      </c>
+      <c r="C787" t="n">
+        <v>1</v>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="B788" t="n">
+        <v>112138</v>
+      </c>
+      <c r="C788" t="n">
+        <v>1</v>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="B789" t="n">
+        <v>112139</v>
+      </c>
+      <c r="C789" t="n">
+        <v>1</v>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="B790" t="n">
+        <v>112140</v>
+      </c>
+      <c r="C790" t="n">
+        <v>1</v>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="B791" t="n">
+        <v>112141</v>
+      </c>
+      <c r="C791" t="n">
+        <v>1</v>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="B792" t="n">
+        <v>112142</v>
+      </c>
+      <c r="C792" t="n">
+        <v>1</v>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="B793" t="n">
+        <v>112143</v>
+      </c>
+      <c r="C793" t="n">
+        <v>1</v>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="B794" t="n">
+        <v>112144</v>
+      </c>
+      <c r="C794" t="n">
+        <v>1</v>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="B795" t="n">
+        <v>112145</v>
+      </c>
+      <c r="C795" t="n">
+        <v>1</v>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="B796" t="n">
+        <v>112146</v>
+      </c>
+      <c r="C796" t="n">
+        <v>1</v>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":114081}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J796"/>
+  <dimension ref="A1:J881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10826,6 +10826,1111 @@
         </is>
       </c>
     </row>
+    <row r="797">
+      <c r="B797" t="n">
+        <v>122009</v>
+      </c>
+      <c r="C797" t="n">
+        <v>1</v>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="B798" t="n">
+        <v>122010</v>
+      </c>
+      <c r="C798" t="n">
+        <v>1</v>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="B799" t="n">
+        <v>122011</v>
+      </c>
+      <c r="C799" t="n">
+        <v>1</v>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="B800" t="n">
+        <v>122012</v>
+      </c>
+      <c r="C800" t="n">
+        <v>1</v>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="B801" t="n">
+        <v>122013</v>
+      </c>
+      <c r="C801" t="n">
+        <v>1</v>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="B802" t="n">
+        <v>122014</v>
+      </c>
+      <c r="C802" t="n">
+        <v>1</v>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="B803" t="n">
+        <v>122015</v>
+      </c>
+      <c r="C803" t="n">
+        <v>1</v>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="B804" t="n">
+        <v>122016</v>
+      </c>
+      <c r="C804" t="n">
+        <v>1</v>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="B805" t="n">
+        <v>122017</v>
+      </c>
+      <c r="C805" t="n">
+        <v>1</v>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="B806" t="n">
+        <v>122018</v>
+      </c>
+      <c r="C806" t="n">
+        <v>1</v>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="B807" t="n">
+        <v>122027</v>
+      </c>
+      <c r="C807" t="n">
+        <v>1</v>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="B808" t="n">
+        <v>122028</v>
+      </c>
+      <c r="C808" t="n">
+        <v>1</v>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="B809" t="n">
+        <v>122029</v>
+      </c>
+      <c r="C809" t="n">
+        <v>1</v>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="B810" t="n">
+        <v>122030</v>
+      </c>
+      <c r="C810" t="n">
+        <v>1</v>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="B811" t="n">
+        <v>122031</v>
+      </c>
+      <c r="C811" t="n">
+        <v>1</v>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="B812" t="n">
+        <v>122032</v>
+      </c>
+      <c r="C812" t="n">
+        <v>1</v>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="B813" t="n">
+        <v>122033</v>
+      </c>
+      <c r="C813" t="n">
+        <v>1</v>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="B814" t="n">
+        <v>122034</v>
+      </c>
+      <c r="C814" t="n">
+        <v>1</v>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="B815" t="n">
+        <v>122035</v>
+      </c>
+      <c r="C815" t="n">
+        <v>1</v>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="B816" t="n">
+        <v>122036</v>
+      </c>
+      <c r="C816" t="n">
+        <v>1</v>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124021}</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="B817" t="n">
+        <v>122045</v>
+      </c>
+      <c r="C817" t="n">
+        <v>1</v>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124022}</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="B818" t="n">
+        <v>122046</v>
+      </c>
+      <c r="C818" t="n">
+        <v>1</v>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="B819" t="n">
+        <v>122047</v>
+      </c>
+      <c r="C819" t="n">
+        <v>1</v>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124024}</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="B820" t="n">
+        <v>122048</v>
+      </c>
+      <c r="C820" t="n">
+        <v>1</v>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="B821" t="n">
+        <v>122049</v>
+      </c>
+      <c r="C821" t="n">
+        <v>1</v>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124026}</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="B822" t="n">
+        <v>122050</v>
+      </c>
+      <c r="C822" t="n">
+        <v>1</v>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124027}</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="B823" t="n">
+        <v>122051</v>
+      </c>
+      <c r="C823" t="n">
+        <v>1</v>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="B824" t="n">
+        <v>122052</v>
+      </c>
+      <c r="C824" t="n">
+        <v>1</v>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124029}</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="B825" t="n">
+        <v>122053</v>
+      </c>
+      <c r="C825" t="n">
+        <v>1</v>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124030}</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="B826" t="n">
+        <v>122054</v>
+      </c>
+      <c r="C826" t="n">
+        <v>1</v>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="B827" t="n">
+        <v>122066</v>
+      </c>
+      <c r="C827" t="n">
+        <v>1</v>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124032}</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="B828" t="n">
+        <v>122067</v>
+      </c>
+      <c r="C828" t="n">
+        <v>1</v>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124033}</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="B829" t="n">
+        <v>122068</v>
+      </c>
+      <c r="C829" t="n">
+        <v>1</v>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="B830" t="n">
+        <v>122069</v>
+      </c>
+      <c r="C830" t="n">
+        <v>1</v>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124035}</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="B831" t="n">
+        <v>122070</v>
+      </c>
+      <c r="C831" t="n">
+        <v>1</v>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124036}</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="B832" t="n">
+        <v>122071</v>
+      </c>
+      <c r="C832" t="n">
+        <v>1</v>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124037}</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="B833" t="n">
+        <v>122072</v>
+      </c>
+      <c r="C833" t="n">
+        <v>1</v>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="B834" t="n">
+        <v>122073</v>
+      </c>
+      <c r="C834" t="n">
+        <v>1</v>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124039}</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="B835" t="n">
+        <v>122074</v>
+      </c>
+      <c r="C835" t="n">
+        <v>1</v>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124040}</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="B836" t="n">
+        <v>122075</v>
+      </c>
+      <c r="C836" t="n">
+        <v>1</v>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="B837" t="n">
+        <v>122087</v>
+      </c>
+      <c r="C837" t="n">
+        <v>1</v>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124042}</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="B838" t="n">
+        <v>122087</v>
+      </c>
+      <c r="C838" t="n">
+        <v>2</v>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="B839" t="n">
+        <v>122088</v>
+      </c>
+      <c r="C839" t="n">
+        <v>1</v>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124044}</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="B840" t="n">
+        <v>122089</v>
+      </c>
+      <c r="C840" t="n">
+        <v>1</v>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124045}</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="B841" t="n">
+        <v>122089</v>
+      </c>
+      <c r="C841" t="n">
+        <v>2</v>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124046}</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="B842" t="n">
+        <v>122090</v>
+      </c>
+      <c r="C842" t="n">
+        <v>1</v>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="B843" t="n">
+        <v>122091</v>
+      </c>
+      <c r="C843" t="n">
+        <v>1</v>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124048}</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="B844" t="n">
+        <v>122091</v>
+      </c>
+      <c r="C844" t="n">
+        <v>2</v>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124049}</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="B845" t="n">
+        <v>122092</v>
+      </c>
+      <c r="C845" t="n">
+        <v>1</v>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124050}</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="B846" t="n">
+        <v>122093</v>
+      </c>
+      <c r="C846" t="n">
+        <v>1</v>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124051}</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="B847" t="n">
+        <v>122093</v>
+      </c>
+      <c r="C847" t="n">
+        <v>2</v>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124052}</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="B848" t="n">
+        <v>122094</v>
+      </c>
+      <c r="C848" t="n">
+        <v>1</v>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="B849" t="n">
+        <v>122095</v>
+      </c>
+      <c r="C849" t="n">
+        <v>1</v>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="B850" t="n">
+        <v>122096</v>
+      </c>
+      <c r="C850" t="n">
+        <v>1</v>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124055}</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="B851" t="n">
+        <v>122096</v>
+      </c>
+      <c r="C851" t="n">
+        <v>2</v>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124056}</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="B852" t="n">
+        <v>122105</v>
+      </c>
+      <c r="C852" t="n">
+        <v>1</v>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124057}</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="B853" t="n">
+        <v>122106</v>
+      </c>
+      <c r="C853" t="n">
+        <v>1</v>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124058}</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="B854" t="n">
+        <v>122107</v>
+      </c>
+      <c r="C854" t="n">
+        <v>1</v>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="B855" t="n">
+        <v>122108</v>
+      </c>
+      <c r="C855" t="n">
+        <v>1</v>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124060}</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="B856" t="n">
+        <v>122109</v>
+      </c>
+      <c r="C856" t="n">
+        <v>1</v>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124061}</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="B857" t="n">
+        <v>122110</v>
+      </c>
+      <c r="C857" t="n">
+        <v>1</v>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124062}</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="B858" t="n">
+        <v>122111</v>
+      </c>
+      <c r="C858" t="n">
+        <v>1</v>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124063}</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="B859" t="n">
+        <v>122112</v>
+      </c>
+      <c r="C859" t="n">
+        <v>1</v>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124064}</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="B860" t="n">
+        <v>122113</v>
+      </c>
+      <c r="C860" t="n">
+        <v>1</v>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="B861" t="n">
+        <v>122114</v>
+      </c>
+      <c r="C861" t="n">
+        <v>1</v>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124066}</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="B862" t="n">
+        <v>122123</v>
+      </c>
+      <c r="C862" t="n">
+        <v>1</v>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124067}</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="B863" t="n">
+        <v>122124</v>
+      </c>
+      <c r="C863" t="n">
+        <v>1</v>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="B864" t="n">
+        <v>122125</v>
+      </c>
+      <c r="C864" t="n">
+        <v>1</v>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124069}</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="B865" t="n">
+        <v>122126</v>
+      </c>
+      <c r="C865" t="n">
+        <v>1</v>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124070}</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="B866" t="n">
+        <v>122127</v>
+      </c>
+      <c r="C866" t="n">
+        <v>1</v>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124071}</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="B867" t="n">
+        <v>122128</v>
+      </c>
+      <c r="C867" t="n">
+        <v>1</v>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="B868" t="n">
+        <v>122129</v>
+      </c>
+      <c r="C868" t="n">
+        <v>1</v>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124073}</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="B869" t="n">
+        <v>122130</v>
+      </c>
+      <c r="C869" t="n">
+        <v>1</v>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="B870" t="n">
+        <v>122131</v>
+      </c>
+      <c r="C870" t="n">
+        <v>1</v>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124075}</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="B871" t="n">
+        <v>122132</v>
+      </c>
+      <c r="C871" t="n">
+        <v>1</v>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124076}</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="B872" t="n">
+        <v>122141</v>
+      </c>
+      <c r="C872" t="n">
+        <v>1</v>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124077}</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="B873" t="n">
+        <v>122142</v>
+      </c>
+      <c r="C873" t="n">
+        <v>1</v>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124078}</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="B874" t="n">
+        <v>122143</v>
+      </c>
+      <c r="C874" t="n">
+        <v>1</v>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124079}</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="B875" t="n">
+        <v>122144</v>
+      </c>
+      <c r="C875" t="n">
+        <v>1</v>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124080}</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="B876" t="n">
+        <v>122145</v>
+      </c>
+      <c r="C876" t="n">
+        <v>1</v>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124081}</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="B877" t="n">
+        <v>122146</v>
+      </c>
+      <c r="C877" t="n">
+        <v>1</v>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124082}</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="B878" t="n">
+        <v>122147</v>
+      </c>
+      <c r="C878" t="n">
+        <v>1</v>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124083}</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="B879" t="n">
+        <v>122148</v>
+      </c>
+      <c r="C879" t="n">
+        <v>1</v>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124084}</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="B880" t="n">
+        <v>122149</v>
+      </c>
+      <c r="C880" t="n">
+        <v>1</v>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124085}</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="B881" t="n">
+        <v>122150</v>
+      </c>
+      <c r="C881" t="n">
+        <v>1</v>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":124086}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/TracePatch.xlsx
+++ b/config/data/TracePatch.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J881"/>
+  <dimension ref="A1:J901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11931,6 +11931,266 @@
         </is>
       </c>
     </row>
+    <row r="882">
+      <c r="B882" t="n">
+        <v>132009</v>
+      </c>
+      <c r="C882" t="n">
+        <v>1</v>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134002}</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="B883" t="n">
+        <v>132010</v>
+      </c>
+      <c r="C883" t="n">
+        <v>1</v>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134003}</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="B884" t="n">
+        <v>132011</v>
+      </c>
+      <c r="C884" t="n">
+        <v>1</v>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="B885" t="n">
+        <v>132012</v>
+      </c>
+      <c r="C885" t="n">
+        <v>1</v>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134005}</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="B886" t="n">
+        <v>132013</v>
+      </c>
+      <c r="C886" t="n">
+        <v>1</v>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134006}</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="B887" t="n">
+        <v>132014</v>
+      </c>
+      <c r="C887" t="n">
+        <v>1</v>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134007}</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="B888" t="n">
+        <v>132015</v>
+      </c>
+      <c r="C888" t="n">
+        <v>1</v>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134008}</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="B889" t="n">
+        <v>132016</v>
+      </c>
+      <c r="C889" t="n">
+        <v>1</v>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="B890" t="n">
+        <v>132017</v>
+      </c>
+      <c r="C890" t="n">
+        <v>1</v>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134010}</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="B891" t="n">
+        <v>132018</v>
+      </c>
+      <c r="C891" t="n">
+        <v>1</v>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="B892" t="n">
+        <v>132027</v>
+      </c>
+      <c r="C892" t="n">
+        <v>1</v>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="B893" t="n">
+        <v>132028</v>
+      </c>
+      <c r="C893" t="n">
+        <v>1</v>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="B894" t="n">
+        <v>132029</v>
+      </c>
+      <c r="C894" t="n">
+        <v>1</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134014}</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="B895" t="n">
+        <v>132030</v>
+      </c>
+      <c r="C895" t="n">
+        <v>1</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="B896" t="n">
+        <v>132031</v>
+      </c>
+      <c r="C896" t="n">
+        <v>1</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="B897" t="n">
+        <v>132032</v>
+      </c>
+      <c r="C897" t="n">
+        <v>1</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134017}</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="B898" t="n">
+        <v>132033</v>
+      </c>
+      <c r="C898" t="n">
+        <v>1</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134018}</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="B899" t="n">
+        <v>132034</v>
+      </c>
+      <c r="C899" t="n">
+        <v>1</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="B900" t="n">
+        <v>132035</v>
+      </c>
+      <c r="C900" t="n">
+        <v>1</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134020}</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="B901" t="n">
+        <v>132036</v>
+      </c>
+      <c r="C901" t="n">
+        <v>1</v>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>{"type":"AddModifier","modifier_identity_id":134021}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
